--- a/Hardware/LoadBoard_250W/JLC_PCBA_BOM-DALI_EVG_LoadBoard(V0.1).xlsx
+++ b/Hardware/LoadBoard_250W/JLC_PCBA_BOM-DALI_EVG_LoadBoard(V0.1).xlsx
@@ -641,7 +641,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F20"/>
+  <dimension ref="A1:F19"/>
   <sheetFormatPr baseColWidth="0" defaultRowHeight="12.75"/>
   <cols>
     <col width="20.2109375" customWidth="1" style="35" min="1" max="2"/>
@@ -902,12 +902,12 @@
     <row r="10">
       <c r="A10" s="32" t="inlineStr">
         <is>
-          <t>KF2EDGR-3.81-4Pin</t>
+          <t>KF2EDGR-3.81-5Pin</t>
         </is>
       </c>
       <c r="B10" s="25" t="inlineStr">
         <is>
-          <t>KF2EDGR-3.81-4Pin</t>
+          <t>KF2EDGR-3.81-5Pin</t>
         </is>
       </c>
       <c r="C10" s="20" t="n"/>
@@ -918,7 +918,7 @@
       </c>
       <c r="E10" s="23" t="inlineStr">
         <is>
-          <t>CONN-TH_4P-P3.81_KF2EDGR-3.81-4P</t>
+          <t>CONN-TH_5P-P3.81_KF2EDGR-3.81-5P</t>
         </is>
       </c>
       <c r="F10" s="20" t="n">
@@ -1043,7 +1043,7 @@
       <c r="C15" s="20" t="n"/>
       <c r="D15" s="23" t="inlineStr">
         <is>
-          <t>R4</t>
+          <t>R4, R16</t>
         </is>
       </c>
       <c r="E15" s="23" t="inlineStr">
@@ -1052,7 +1052,7 @@
         </is>
       </c>
       <c r="F15" s="20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16">
@@ -1136,52 +1136,26 @@
     <row r="19">
       <c r="A19" s="32" t="inlineStr">
         <is>
-          <t>470</t>
+          <t>UCC27517DBVR</t>
         </is>
       </c>
       <c r="B19" s="25" t="inlineStr">
         <is>
-          <t>Resistor</t>
-        </is>
-      </c>
-      <c r="C19" s="20" t="n"/>
+          <t>4-A/4-A single-channel gate driver with 5-V UVLO and 13-ns prop delay in SOT-23 package</t>
+        </is>
+      </c>
+      <c r="C19" s="23" t="inlineStr"/>
       <c r="D19" s="23" t="inlineStr">
         <is>
-          <t>R16</t>
+          <t>U1, U2, U3, U4</t>
         </is>
       </c>
       <c r="E19" s="23" t="inlineStr">
         <is>
-          <t>R1206</t>
+          <t>SOT23-5</t>
         </is>
       </c>
       <c r="F19" s="20" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="32" t="inlineStr">
-        <is>
-          <t>UCC27517DBVR</t>
-        </is>
-      </c>
-      <c r="B20" s="25" t="inlineStr">
-        <is>
-          <t>4-A/4-A single-channel gate driver with 5-V UVLO and 13-ns prop delay in SOT-23 package</t>
-        </is>
-      </c>
-      <c r="C20" s="23" t="inlineStr"/>
-      <c r="D20" s="23" t="inlineStr">
-        <is>
-          <t>U1, U2, U3, U4</t>
-        </is>
-      </c>
-      <c r="E20" s="23" t="inlineStr">
-        <is>
-          <t>SOT23-5</t>
-        </is>
-      </c>
-      <c r="F20" s="20" t="n">
         <v>4</v>
       </c>
     </row>
